--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/feb-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/feb-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>63090.6</v>
+        <v>62576.9</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>651.99</v>
+        <v>646.6799999999999</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>35461.09</v>
+        <v>35616.04</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>32758.58</v>
+        <v>32901.72</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>29725.38</v>
+        <v>29574.68</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>47317.95</v>
+        <v>47704.99</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>48025.7</v>
+        <v>48311.88</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>61270.68</v>
+        <v>61786.7</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>67943.72</v>
+        <v>68515.95</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1567.15</v>
+        <v>1565.68</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>38222.95</v>
+        <v>38186.96</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>8189.65</v>
+        <v>8181.93</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>7229.13</v>
+        <v>7221.2</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>17440.91</v>
+        <v>17394.98</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>10717.31</v>
+        <v>10689.09</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>37813.92</v>
+        <v>37714.34</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1287.11</v>
+        <v>1295.55</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>9706.25</v>
+        <v>9730.34</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/feb-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/feb-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/feb-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/feb-2026.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Servicio de bienestar UAF</t>
+          <t>UNIDAD DE ANALISIS FINANCIERO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Servicio de bienestar del personal del CNTV</t>
+          <t>CONSEJO NACIONAL DE TELEVISION</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>COMISIÓN CHILENA DEL COBRE - COCHILCO</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar Dirección de Compras y Contratación Pública</t>
+          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/feb-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/feb-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/feb-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/feb-2026.xlsx
@@ -859,7 +859,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
